--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -951,6 +951,394 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128846810</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Glotternskogens naturreservat, Glotternskogens naturreservat, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>568211</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6506247</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128846019</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95944</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Glotternskogens naturreservat, Glotternskogens naturreservat, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>568340</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6506269</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128846794</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95933</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Glotternskogens naturreservat, Glotternskogens naturreservat, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>568211</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6506247</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128845628</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92812</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Glotternskogens naturreservat, Glotternskogens naturreservat, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>568336</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6506361</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>95944</v>
+        <v>95950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>95933</v>
+        <v>95939</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>128845628</v>
       </c>
       <c r="B7" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>95950</v>
+        <v>95957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>95939</v>
+        <v>95946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>128845628</v>
       </c>
       <c r="B7" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,21 +1257,12 @@
       <c r="E7" t="n">
         <v>5449</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1330,6 +1330,117 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128926911</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Glotternskogen, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>568349</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6506356</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>95957</v>
+        <v>95961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>95946</v>
+        <v>95950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>128845628</v>
       </c>
       <c r="B7" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128926911</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>95961</v>
+        <v>95968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>95950</v>
+        <v>95957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>128845628</v>
       </c>
       <c r="B7" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128926911</v>
       </c>
       <c r="B8" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>95976</v>
+        <v>95981</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>95965</v>
+        <v>95970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>128845628</v>
       </c>
       <c r="B7" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128926911</v>
       </c>
       <c r="B8" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>95981</v>
+        <v>95984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>95970</v>
+        <v>95973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>128845628</v>
       </c>
       <c r="B7" t="n">
-        <v>92845</v>
+        <v>92848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128926911</v>
       </c>
       <c r="B8" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>95984</v>
+        <v>95994</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>95973</v>
+        <v>95983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>128845628</v>
       </c>
       <c r="B7" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128926911</v>
       </c>
       <c r="B8" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>95994</v>
+        <v>96001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>95983</v>
+        <v>95990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>128845628</v>
       </c>
       <c r="B7" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128926911</v>
       </c>
       <c r="B8" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>96001</v>
+        <v>96003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>95990</v>
+        <v>95992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>128845628</v>
       </c>
       <c r="B7" t="n">
-        <v>92862</v>
+        <v>92864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128926911</v>
       </c>
       <c r="B8" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>96003</v>
+        <v>96029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>95992</v>
+        <v>96018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>128845628</v>
       </c>
       <c r="B7" t="n">
-        <v>92864</v>
+        <v>92850</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128926911</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>96029</v>
+        <v>96030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>96018</v>
+        <v>96019</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>128845628</v>
       </c>
       <c r="B7" t="n">
-        <v>92850</v>
+        <v>92851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,9 +1257,14 @@
       <c r="E7" t="n">
         <v>5449</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp agg.</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
+          <t>Phellodon niger s.lat.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1335,7 +1340,7 @@
         <v>128926911</v>
       </c>
       <c r="B8" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>96030</v>
+        <v>96031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>96019</v>
+        <v>96020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>128846810</v>
       </c>
       <c r="B4" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>128846019</v>
       </c>
       <c r="B5" t="n">
-        <v>96031</v>
+        <v>96035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128846794</v>
       </c>
       <c r="B6" t="n">
-        <v>96020</v>
+        <v>96024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>128845628</v>
       </c>
       <c r="B7" t="n">
-        <v>92851</v>
+        <v>92854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>128926911</v>
       </c>
       <c r="B8" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1340,7 +1340,7 @@
         <v>128926911</v>
       </c>
       <c r="B8" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1340,7 +1340,7 @@
         <v>128926911</v>
       </c>
       <c r="B8" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1446,6 +1446,131 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129866786</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Karlsdal VNV 900 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>568228</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6506298</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>E-Nor-0851</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
         <v>129866786</v>
       </c>
       <c r="B9" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
         <v>129866786</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
         <v>129866786</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
         <v>129866786</v>
       </c>
       <c r="B9" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
         <v>129866786</v>
       </c>
       <c r="B9" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
         <v>129866786</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
         <v>129866786</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1571,6 +1571,103 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131759066</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96354</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Glotternskogens naturreservat, Glotternskogens naturreservat, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>568348</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6506391</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1576,7 +1576,7 @@
         <v>131759066</v>
       </c>
       <c r="B10" t="n">
-        <v>96354</v>
+        <v>96357</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1576,7 +1576,7 @@
         <v>131759066</v>
       </c>
       <c r="B10" t="n">
-        <v>96357</v>
+        <v>96363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1576,7 +1576,7 @@
         <v>131759066</v>
       </c>
       <c r="B10" t="n">
-        <v>96363</v>
+        <v>96366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1576,7 +1576,7 @@
         <v>131759066</v>
       </c>
       <c r="B10" t="n">
-        <v>96366</v>
+        <v>96371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -1576,7 +1576,7 @@
         <v>131759066</v>
       </c>
       <c r="B10" t="n">
-        <v>96414</v>
+        <v>96417</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,69 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124075652</v>
+        <v>128846019</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råsjövägen-Lomgölsvägen ONO 740 m, Ög</t>
+          <t>Glotternskogens naturreservat, Glotternskogens naturreservat, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568249</v>
+        <v>568340</v>
       </c>
       <c r="R2" t="n">
-        <v>6506285</v>
+        <v>6506269</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,39 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124075239</v>
+        <v>131759066</v>
       </c>
       <c r="B3" t="n">
-        <v>56482</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,58 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100088</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karlsdal V 720 m, Ög</t>
+          <t>Glotternskogens naturreservat, Glotternskogens naturreservat, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568315</v>
+        <v>568348</v>
       </c>
       <c r="R3" t="n">
-        <v>6506185</v>
+        <v>6506391</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:50</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:50</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,39 +851,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog nära sjö</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128846810</v>
+        <v>128846794</v>
       </c>
       <c r="B4" t="n">
-        <v>100899</v>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1050,48 +966,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128846019</v>
+        <v>128920400</v>
       </c>
       <c r="B5" t="n">
-        <v>96035</v>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2667</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Glotternskogens naturreservat, Glotternskogens naturreservat, Ög</t>
+          <t>Glotternskogen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568340</v>
+        <v>568363</v>
       </c>
       <c r="R5" t="n">
-        <v>6506269</v>
+        <v>6506357</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,77 +1037,91 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128846794</v>
+        <v>128926911</v>
       </c>
       <c r="B6" t="n">
-        <v>96024</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Glotternskogens naturreservat, Glotternskogens naturreservat, Ög</t>
+          <t>Glotternskogen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568211</v>
+        <v>568349</v>
       </c>
       <c r="R6" t="n">
-        <v>6506247</v>
+        <v>6506356</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,39 +1148,50 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845628</v>
+        <v>128845974</v>
       </c>
       <c r="B7" t="n">
-        <v>92854</v>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,19 +1199,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,13 +1223,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568336</v>
+        <v>568339</v>
       </c>
       <c r="R7" t="n">
-        <v>6506361</v>
+        <v>6506280</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,48 +1285,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128926911</v>
+        <v>128845828</v>
       </c>
       <c r="B8" t="n">
-        <v>92831</v>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Glotternskogen, Ög</t>
+          <t>Glotternskogens naturreservat, Glotternskogens naturreservat, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568349</v>
+        <v>568342</v>
       </c>
       <c r="R8" t="n">
-        <v>6506356</v>
+        <v>6506338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,102 +1353,98 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129866786</v>
+        <v>124075239</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>56895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100088</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Karlsdal VNV 900 m, Ög</t>
+          <t>Karlsdal V 720 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568228</v>
+        <v>568315</v>
       </c>
       <c r="R9" t="n">
-        <v>6506298</v>
+        <v>6506185</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,39 +1466,50 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>E-Nor-0851</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog nära sjö</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1565,56 +1517,68 @@
           <t>Mirjam Ideström</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131759066</v>
+        <v>115308714</v>
       </c>
       <c r="B10" t="n">
-        <v>96417</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Glotternskogens naturreservat, Glotternskogens naturreservat, Ög</t>
+          <t>Karlsdal VNV 900 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568348</v>
+        <v>568217</v>
       </c>
       <c r="R10" t="n">
-        <v>6506391</v>
+        <v>6506300</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,12 +1602,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 150 skott</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,21 +1621,393 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Mestadels gran</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121264448</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Karlsdal VNV 900 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>568228</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6506298</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>E-Nor-0851</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 150 skott</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Mestadels gran</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124075652</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Råsjövägen-Lomgölsvägen ONO 740 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>568249</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6506285</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128846810</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Glotternskogens naturreservat, Glotternskogens naturreservat, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>568211</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6506247</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Eva Siljeholm</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Eva Siljeholm</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45509-2025 artfynd.xlsx
+++ b/artfynd/A 45509-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128846019</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131759066</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128846794</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920400</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128926911</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845974</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845828</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124075239</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1647,6 +1692,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115308714</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121264448</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1911,6 +1966,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124075652</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2008,8 +2068,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128846810</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>